--- a/261016_회의록_수입참치캔검토.xlsx
+++ b/261016_회의록_수입참치캔검토.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="회의록" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'회의록'!$A$1:$D$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'회의록'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,13 +562,12 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
     </row>
-    <row r="6" ht="84" customHeight="1">
+    <row r="6" ht="74" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>· 태국 공장산 신규 참치캔 시식 결과: 동원 대비 비린내가 적고 색·입자가 좋아 "클레임 우려 낮다"는 평가
 · 공급 제시가 12,500원(VAT 별도), 목표 매입가는 13,000원 중반 → 단가 추가 조정 필요
-· 입고는 승인 후 약 4주(정밀검사 걸리면 6주 안팎) → 다음 주 목·금까지 판매처 의견 취합 후 피드백
-· 파스타(수입) 건은 1월 중순 입고 예정, 주문 수량은 월요일까지 회신 필요</t>
+· 입고는 승인 후 약 4주(정밀검사 걸리면 6주 안팎) → 다음 주 목·금까지 판매처 의견 취합 후 피드백</t>
         </is>
       </c>
     </row>
@@ -600,7 +599,7 @@
       </c>
       <c r="D9" s="7" t="n"/>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>품질 평가</t>
@@ -618,7 +617,7 @@
       </c>
       <c r="D10" s="7" t="n"/>
     </row>
-    <row r="11" ht="58" customHeight="1">
+    <row r="11" ht="80" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>제품 구성(안)</t>
@@ -636,7 +635,7 @@
       </c>
       <c r="D11" s="7" t="n"/>
     </row>
-    <row r="12" ht="40" customHeight="1">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>원가 절감안</t>
@@ -654,7 +653,7 @@
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
-    <row r="13" ht="58" customHeight="1">
+    <row r="13" ht="64" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>가격</t>
@@ -672,7 +671,7 @@
       </c>
       <c r="D13" s="7" t="n"/>
     </row>
-    <row r="14" ht="40" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>마진</t>
@@ -690,7 +689,7 @@
       </c>
       <c r="D14" s="7" t="n"/>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>입고 일정</t>
@@ -708,99 +707,101 @@
       </c>
       <c r="D15" s="7" t="n"/>
     </row>
-    <row r="16" ht="40" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
+          <t>캔 품질</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>샘플 캔은 안쪽이 쉽게 긁힘(동원 캔은 덜함). 급식 민감 고객은 내용물과 접촉 시 사용 안 한다는 의견</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>샘플 캔 한정 여부 확인</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
           <t>판매처 전략</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>대기업 급식은 원가 위주라 해당 제품 사용 가능성 낮음. 마트·도매·외식·고급 사업장 중심으로 제안</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>마트팀 관심 있음(마트 400여 곳)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n"/>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>파스타(수입)</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>1월 중순 입고 예정(선박). 항공 운송은 6팔레트 단위로 비용 부담 커 비효율. 수입 발주를 위해 월요일까지 수량 회신 필요</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>금액 수치 확인 필요</t>
-        </is>
-      </c>
       <c r="D17" s="7" t="n"/>
     </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>참고 사례</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>수입 파스타에서 벌레(바구미)가 나와 센터 폐기·청구 이슈 발생. 온도·습도 관리 중요</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>금액은 녹취상 불명확</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n"/>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>3. 후속 조치</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>3. 후속 조치</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>담당</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>기한</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>샘플 추가 확보(약 10개 요청) 및 판매처 시식·사진 공유</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>샘플 추가 확보(약 10개 요청) 및 판매처 시식·사진 공유</t>
+          <t>경로별(마트·도매 등) 가격 적정성 조사 → 매입가 이상 가능 여부 확인</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -810,17 +811,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>다음 주 목·금</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>경로별(마트·도매 등) 가격 적정성 조사 → 매입가 이상 가능 여부 확인</t>
+          <t>판매처 의견 취합 후 공급사에 피드백, 단가 추가 조정 요청</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -836,11 +837,11 @@
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>판매처 의견 취합 후 공급사에 피드백, 단가 추가 조정 요청</t>
+          <t>샘플 캔 내면 긁힘 원인(샘플 한정/양산 동일) 공급사에 확인</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -850,52 +851,31 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>다음 주 목·금</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>파스타 주문 수량 회신(수입 발주 마감)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>영업사원/팀</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>월요일</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+          <t>확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>4. 확인 필요 (녹취 변환 오류 가능)</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="72" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="68" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>· 회의 일시·참석자 이름(녹취는 "참석자 1~5"로만 표기)
-· 가격 수치: 12,500원/13,750원/17,600원/15,000원은 변환 오류 가능성이 있어 원본 대조 필요
-· 파스타 항공 운송 금액, 벌레 사건 청구·폐기 금액
+· 가격 수치: 12,500원/13,750원/15,000원은 변환 오류 가능성이 있어 원본 대조 필요
 · 제품 구성 용어(슈레드·플레이크·"빠시")의 정확한 의미</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="C12:D12"/>
@@ -905,14 +885,13 @@
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A28:D28"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
